--- a/jpcore-r4/develop/StructureDefinition-jp-obsrevation-electrocardiogram-machinaryinterpretation.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-obsrevation-electrocardiogram-machinaryinterpretation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="111">
   <si>
     <t>Property</t>
   </si>
@@ -262,7 +262,7 @@
 </t>
   </si>
   <si>
-    <t>機械判定</t>
+    <t>機械判定された所見・解釈の有無</t>
   </si>
   <si>
     <t>心電図検査の所見が機械的に判定されたものであるかどうかを示す</t>
@@ -345,6 +345,9 @@
   <si>
     <t xml:space="preserve">boolean
 </t>
+  </si>
+  <si>
+    <t>機械判定の有無</t>
   </si>
   <si>
     <t>心電図検査が機械的に判定されたものであるかどうかを示す</t>
@@ -1264,10 +1267,10 @@
         <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1330,7 +1333,7 @@
         <v>78</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>105</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-obsrevation-electrocardiogram-machinaryinterpretation.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-obsrevation-electrocardiogram-machinaryinterpretation.xlsx
@@ -347,7 +347,7 @@
 </t>
   </si>
   <si>
-    <t>機械判定の有無</t>
+    <t>機械判定所見の有無</t>
   </si>
   <si>
     <t>心電図検査が機械的に判定されたものであるかどうかを示す</t>
